--- a/artefacts/engine_test_scenarios.xlsx
+++ b/artefacts/engine_test_scenarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\forcasting model\artefacts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2206B589-0243-4C53-BF80-05EA3B42836B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE44FBD1-999C-4862-A463-314E99B1EEFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3510" yWindow="3510" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
